--- a/backend/rent.xlsx
+++ b/backend/rent.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -439,15 +439,84 @@
         <v>2026-08-30</v>
       </c>
       <c r="F2" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="G2" t="str">
+        <v>คืนแล้ว</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>800080000055</v>
+      </c>
+      <c r="B3" t="str">
+        <v>นาง คนอง ม้วนเรียน</v>
+      </c>
+      <c r="C3" t="str">
+        <v>ขค.7อ.(บ)943/2569 ลว.28/8/2569 ศูนย์หนี้</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="E3" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="F3" t="str">
         <v/>
       </c>
-      <c r="G2" t="str">
+      <c r="G3" t="str">
+        <v>ยืมอยู่</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>800102199588</v>
+      </c>
+      <c r="B4" t="str">
+        <v>นางสาว จุฑามาศ สอนงอก</v>
+      </c>
+      <c r="C4" t="str">
+        <v>ขค.7อ.103/2569 ลว.3/2/2569 ศูนย์หนี้ ปิดหนี้ไวไปต่อได้</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="E4" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v>ยืมอยู่</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>800094988923</v>
+      </c>
+      <c r="B5" t="str">
+        <v>นางสาว หมาย วิชาฟอง</v>
+      </c>
+      <c r="C5" t="str">
+        <v>ขค.7อ.(บ)943/2569 ลว.28/8/2569 ศูนย์หนี้</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="E5" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
         <v>ยืมอยู่</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G5"/>
   </ignoredErrors>
 </worksheet>
 </file>